--- a/sample/docs/tabular/loss-run.xlsx
+++ b/sample/docs/tabular/loss-run.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="€#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -485,22 +485,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HO-0000001</t>
+          <t>HH-0000001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Homeowners</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2023-12-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>theft</t>
+          <t>kitchen fire</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>45350</v>
+        <v>41050</v>
       </c>
     </row>
     <row r="4">
@@ -523,34 +523,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HO-0000003</t>
+          <t>HH-0000004</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Homeowners</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>liability slip</t>
+          <t>theft</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
+        <v>49900</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>23950</v>
+        <v>10561.12</v>
       </c>
     </row>
     <row r="5">
@@ -561,34 +561,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PA-0000002</t>
+          <t>COM-0000005</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Personal Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-12-23</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>vandalism</t>
+          <t>equipment breakdown</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>28900</v>
+        <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>8635.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -599,34 +599,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PA-0000004</t>
+          <t>COM-0000005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Personal Auto</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>single vehicle</t>
+          <t>slip and fall</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="7">
@@ -637,22 +637,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PA-0000005</t>
+          <t>HH-0000004</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Personal Auto</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>single vehicle</t>
+          <t>theft</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>18350</v>
+        <v>12850</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>5813.86</v>
+        <v>4474.47</v>
       </c>
     </row>
   </sheetData>

--- a/sample/docs/tabular/loss-run.xlsx
+++ b/sample/docs/tabular/loss-run.xlsx
@@ -485,22 +485,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HH-0000001</t>
+          <t>COM-0000003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2023-12-26</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>kitchen fire</t>
+          <t>slip and fall</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>41050</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="4">
@@ -523,22 +523,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HH-0000004</t>
+          <t>COM-0000004</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>theft</t>
+          <t>burglary</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>49900</v>
+        <v>53950</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>10561.12</v>
+        <v>19694.51</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>COM-0000005</t>
+          <t>COM-0000003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>equipment breakdown</t>
+          <t>burglary</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -599,22 +599,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COM-0000005</t>
+          <t>MOT-0000005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Motor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>slip and fall</t>
+          <t>rear end collision</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>8550</v>
+        <v>48050</v>
       </c>
     </row>
     <row r="7">
@@ -637,34 +637,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HH-0000004</t>
+          <t>COM-0000003</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2023-12-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>theft</t>
+          <t>business interruption</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>12850</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>4474.47</v>
+        <v>48950</v>
       </c>
     </row>
   </sheetData>

--- a/sample/docs/tabular/loss-run.xlsx
+++ b/sample/docs/tabular/loss-run.xlsx
@@ -495,12 +495,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>slip and fall</t>
+          <t>burglary</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>8550</v>
+        <v>23700</v>
       </c>
     </row>
     <row r="4">
@@ -523,22 +523,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>COM-0000004</t>
+          <t>HH-0000001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>burglary</t>
+          <t>theft</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>53950</v>
+        <v>12850</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>19694.51</v>
+        <v>4474.47</v>
       </c>
     </row>
     <row r="5">

--- a/sample/docs/tabular/loss-run.xlsx
+++ b/sample/docs/tabular/loss-run.xlsx
@@ -485,22 +485,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HH-0000001</t>
+          <t>COM-0000003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2023-12-26</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>kitchen fire</t>
+          <t>burglary</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>41050</v>
+        <v>23700</v>
       </c>
     </row>
     <row r="4">
@@ -523,7 +523,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HH-0000004</t>
+          <t>HH-0000001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>49900</v>
+        <v>12850</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>10561.12</v>
+        <v>4474.47</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +561,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>COM-0000005</t>
+          <t>COM-0000003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>equipment breakdown</t>
+          <t>burglary</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -599,22 +599,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COM-0000005</t>
+          <t>MOT-0000005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Motor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>slip and fall</t>
+          <t>rear end collision</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>8550</v>
+        <v>48050</v>
       </c>
     </row>
     <row r="7">
@@ -637,34 +637,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HH-0000004</t>
+          <t>COM-0000003</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2023-12-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>theft</t>
+          <t>business interruption</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>12850</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>4474.47</v>
+        <v>48950</v>
       </c>
     </row>
   </sheetData>

--- a/sample/docs/tabular/loss-run.xlsx
+++ b/sample/docs/tabular/loss-run.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>COM-0000003</t>
+          <t>COM-0000001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -495,12 +495,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>burglary</t>
+          <t>business interruption</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>23700</v>
+        <v>10650</v>
       </c>
     </row>
     <row r="4">
@@ -523,22 +523,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HH-0000001</t>
+          <t>MOT-0000002</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Motor</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>theft</t>
+          <t>vandalism</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12850</v>
+        <v>2050</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>4474.47</v>
+        <v>491.13</v>
       </c>
     </row>
     <row r="5">
@@ -561,22 +561,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>COM-0000003</t>
+          <t>MOT-0000004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Motor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>burglary</t>
+          <t>theft</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MOT-0000005</t>
+          <t>MOT-0000002</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -619,14 +619,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>48050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -637,22 +637,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>COM-0000003</t>
+          <t>MOT-0000004</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Motor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2023-12-14</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>business interruption</t>
+          <t>hail</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
